--- a/ZhangInvest/现有接口.xlsx
+++ b/ZhangInvest/现有接口.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\pythonProject\ZhangInvest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3C2C54-148E-44FD-AA41-ED6F8620E648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3581581-FAB3-4092-A766-384E4D82B6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10450" yWindow="2730" windowWidth="27220" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14390" yWindow="2810" windowWidth="24220" windowHeight="16450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="79">
   <si>
     <t>分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -291,6 +291,60 @@
   </si>
   <si>
     <t>获取基金历史净值（目前用于获取近3天）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股票数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦蕊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取股票代码及名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://api.mairui.club/hslt/list/b997d4403688d5e66a</t>
+  </si>
+  <si>
+    <t>新浪财经</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯财经</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被禁用</t>
+  </si>
+  <si>
+    <t>https://hq.sinajs.cn/list={stock_code},{stock_code}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stock_code=指数/股票代码，道琼斯："gb_dji"，标普500："gb_inx"，纳斯达克："gb_ixic"，上证指数："s_sh000001"，深证成指："s_sz399001"，创业板指："s_sz399006"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://qt.gtimg.cn/q={stock_code},{stock_code}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stock_code=指数/股票代码，道琼斯："usDJI"，标普500："usINX"，纳斯达克："usIXIC"，上证指数："sh000001"，深证成指："sz399001"，创业板指："sz399006"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://stock.xueqiu.com/v5/stock/realtime/quotec.json?symbol={stock_code},{stock_code}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stock_code=指数/股票代码，道琼斯：".DJI"，标普500：".INX"，纳斯达克：".IXIC"，上证指数："SH000001"，深证成指："SZ399001"，创业板指："SZ399006"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -298,7 +352,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,6 +371,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -343,10 +404,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -668,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="2" customWidth="1"/>
@@ -931,7 +995,7 @@
       <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -944,7 +1008,7 @@
         <v>54</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="I9" t="s">
         <v>45</v>
@@ -1044,6 +1108,12 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
       <c r="C13" s="2" t="s">
         <v>52</v>
       </c>
@@ -1066,14 +1136,131 @@
         <v>62</v>
       </c>
     </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576 H2:H1048576" xr:uid="{4A19B9BE-F988-4EFB-83AA-4C7C1AEC0D29}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{4A19B9BE-F988-4EFB-83AA-4C7C1AEC0D29}">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{0336E56A-D373-41F4-B249-33EA4DBE5D31}">
       <formula1>"高,中,低"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{ED4E83A7-AD0A-44B0-8A8C-4CD519C92E12}">
+      <formula1>"是,否,被禁用"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -1089,11 +1276,15 @@
     <hyperlink ref="J11" r:id="rId10" xr:uid="{59C2A785-3353-484C-ADFA-3A76B3B852AF}"/>
     <hyperlink ref="J12" r:id="rId11" xr:uid="{A9AFC760-201D-489E-8123-43156CFA6462}"/>
     <hyperlink ref="J13" r:id="rId12" xr:uid="{C43489F8-2E3E-40A0-981C-8CC646FB72AC}"/>
+    <hyperlink ref="J14" r:id="rId13" xr:uid="{28FBBACB-2CBE-4C6F-BAF8-CE52870B02F6}"/>
+    <hyperlink ref="J15" r:id="rId14" xr:uid="{145F8E94-33FA-419B-9C1B-33D0421ED877}"/>
+    <hyperlink ref="J16" r:id="rId15" xr:uid="{66109D7C-04ED-46C4-BA08-E45F52D1FBD9}"/>
+    <hyperlink ref="J17" r:id="rId16" xr:uid="{5C63088D-4C8C-4932-8522-46DBC0AF289C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId17"/>
   <tableParts count="1">
-    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId18"/>
   </tableParts>
 </worksheet>
 </file>